--- a/data/review/hkm037-item1-2026-10-23/item1-decisions.xlsx
+++ b/data/review/hkm037-item1-2026-10-23/item1-decisions.xlsx
@@ -967,8 +967,16 @@
           <t>صورة آلة كاتبة قديمة؛ النص مقروء لكن المسافات بين الكلمات ملتصقة في مواضع (نُقلت كما تظهر) والهمزات غالبًا محذوفة في الأصل. المادة موجودة في حكيم، مع فرق واحد ظاهر: الصورة «على الحالة الراهنة» وحكيم «على حالة الراهنة». الملاحظة تقول «المرسوم الملكي رقم (2)» والصورة «م/2».</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -1065,8 +1073,16 @@
           <t>نص حكيم مطابق لهذا النص مع إضافة القرار 17/1444هـ (الفقرة 8 وزارة النقل وإعادة الترقيم). جملة «ويبدأ العمل بهذا البند...» حكم نفاذ لا جزء من نص المادة، وعُدلت بالقرار 17/1444هـ (ثانياً) لتكون «من تاريخ 1/1/1444هـ». نص الهيئة المعروض قديم.</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -1163,8 +1179,16 @@
           <t>الفقرة 8 موجودة في حكيم وأُعيد ترقيم فقرة القطاع الخاص إلى 9. النص في الأداة بلا كلمة «عضواً» وكذا في حكيم.</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -1254,8 +1278,16 @@
           <t>نص حكيم في الفقرة (11): "وتفويض الرئيس التنفيذي بالتوقيع عليها" وكلمة المحافظ غائبة. نهاية سطر البند الثاني (الخامسة)/(السادسة) مقروءة بصعوبة في الأصل لكنها واضحة بعد التكبير.</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -1337,8 +1369,16 @@
           <t>نص حكيم ينتهي بالفقرة (16) ولا توجد فيه فقرة (17)، فالأثر ظاهر (سواء لأن الإضافة لم تُحقن أصلًا أو لأن الحذف طُبق). نص الفقرة (17) المحذوفة غير موجود في هذه الصور.</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1445,8 +1485,16 @@
           <t>نص حكيم يبدأ بـ«يكون للصندوق محافظ يعين بأمر ملكي، ويعد المسؤول التنفيذي...» والعبارة القديمة غائبة؛ الأثر ظاهر.</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1541,8 +1589,16 @@
           <t>الأثر مركّب (حذف عبارتين وإضافة عبارتين). نص حكيم خالٍ من ممثل الشركة السعودية للكهرباء ومن ممثل أرامكو في الفقرة (4)، وفيه ممثلا وزارتي الطاقة والصناعة. نص الملاحظة في الهيئة يقول «شركة أرامكو،» بينما الأداة «شركة أرامكو السعودية،». نص الهيئة المعروض قديم.</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -1629,8 +1685,16 @@
           <t>نص حكيم: «الخدمات: الخدمات التي تنظمها الهيئة في نشاط الكهرباء.» ولا يوجد فيه تعريف «نشاط المياه»، والاسم في حكيم «الهيئة السعودية لتنظيم الكهرباء»؛ الأثر ظاهر.</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -1721,8 +1785,16 @@
           <t>نص حكيم: «أ- رفع كفاءة محطات توليد الكهرباء ... ج- تشجيع مشاريع محطات توليد الكهرباء العالية الكفاءة» و«لترشيد استهلاك الكهرباء» دون «أو الماء»، ولا وجود لعبارة «إنتاج المياه والكهرباء»؛ الأثر ظاهر.</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1812,8 +1884,16 @@
           <t>hk_text يبدأ بـ«يكون للهيئة مجلس إدارة يشكل من رئيس يعين بأمر من رئيس مجلس الوزراء» والعبارة القديمة غائبة.</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1900,8 +1980,16 @@
           <t>الملاحظة لا تذكر رقم الأداة؛ المطابقة بالمضمون مع القرار (11) لعام 1439هـ، والبند نفسه مقروء كاملًا. نص حكيم ينتهي بـ«لجنة المراجعة: لدراسة الجوانب المتعلقة بالمجالات الرقابية للهيئة.» فالأثر ظاهر.</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -2146,8 +2234,16 @@
           <t>hk_text ما زال «وترتبط إداريا بوزير المالية». تنبيه مهم: قرار مجلس الوزراء رقم (440) وتاريخ 1437/10/20هـ (الصور 37089388 ص3) نص في البند خامساً: «إحلال عبارة "بوزير الخدمة المدنية" محل عبارة "بوزارة الخدمة المدنية" الواردة في المادة (الثانية) من تنظيم المؤسسة العامة للتقاعد ... المعدلة بموجب البند (أولاً) من قرار مجلس الوزراء رقم (461) وتاريخ 1436/11/2هـ»؛ فالصيغة النافذة بعد التعديلين «بوزير الخدمة المدنية».</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -2238,8 +2334,16 @@
           <t>الملاحظة لا تسمي الأداة، والصور للقرار 212 وفيه البند ثانياً بعينه. hk_text ما زال يبدأ بـ«يكون للهيئة رئيس بالمرتبة الممتازة».</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -2329,8 +2433,16 @@
           <t>نص حكيم ما زال: "1- المحافظ عضواً ونائباً للرئيس". تنبيه: القرار نفسه في البند (أولاً/5) نص على "إحلال عبارة (الرئيس التنفيذي) محل كلمة (المحافظ) أينما وردت في التنظيم." وهذا يمس الفقرة (1) والبند (ثالثاً) من المادة نفسها في حكيم ("فيما عدا الرئيس والمحافظ") وليس له ملاحظة في هذه الحزمة.</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -2420,8 +2532,16 @@
           <t>نص حكيم ما زال يتضمن «تحدد فيه مكافآتهم». تنبيه: الفقرة (1) في حكيم هي الصيغة الأصلية (برئاسة محافظ الهيئة العامة للاستثمار)، بينما عُدّلت بالأمرين الملكيين أ/22 بتاريخ 1437/2/7هـ وأ/324 بتاريخ 1440/9/11هـ (صفحتا 89f873c2 و473256a0) إلى «يكون للهيئة مجلس إدارة يُعيّن رئيسه بأمر ملكي، وعضوية عدد من ذوي الخبرة والاختصاص من القطاعين الحكومي والخاص، يرشحهم رئيس المجلس، ويصدر بتعيينهم أمر ملكي تحدد فيه مكافآتهم»؛ فالحذف ينبغي أن يقع على الصيغة المحدثة.</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -2515,8 +2635,16 @@
           <t>hk_text (البند السادس عشر بالعدّ: «تكليف أعضاء مجلس الهيئة ... المعينين وفقاً للفقرة (ج) من المادة (الرابعة)») ما زال بالعبارة القديمة. تنبيه: الصور c092fa97 فيها قرار مجلس الوزراء رقم (237) وتاريخ 1437/6/5هـ يعدّل الفقرتين (15) و(17) من المادة الخامسة ويحل كلمة (الملك) محل (رئيس مجلس الوزراء) أينما وردت — وhk_text لم يُطبق ذلك أيضًا (ما زال «بالاتفاق مع وزارة الخدمة المدنية، ووزارة المالية» و«رئيس مجلس الوزراء»).</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -2611,8 +2739,16 @@
           <t>نص حكيم ما زال (180) يوماً.</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -2698,8 +2834,16 @@
           <t>الملاحظة لا تذكر الأداة؛ نصها يطابق البند المقروء في المرسوم م/134. نص حكيم ما زال يتضمن «محل إقامة المرأة المتزوجة هو محل إقامة زوجها...»؛ الأثر (حذف حكم المرأة المتزوجة) غير ظاهر.</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -2792,8 +2936,16 @@
           <t>الملاحظة لا تذكر الأداة؛ نصها يطابق البند المقروء في المرسوم م/134. نص حكيم هو الصيغة القديمة («والد الطفل إذا كان موجودا...» و«سبعة عشر عاما»)؛ الأثر غير ظاهر. في الصورة «ثمانية عشر عاماً» بينما الملاحظة «ثمانية عشرة».</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -2880,8 +3032,16 @@
           <t>الملاحظة لا تذكر الأداة؛ نصها يطابق البند المقروء في المرسوم م/134. نص حكيم هو الصيغة القديمة («تقع مسئولية التبليغ ... على الزوج»)؛ الأثر غير ظاهر.</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -2967,8 +3127,16 @@
           <t>الملاحظة لا تذكر الأداة؛ نصها يطابق البند المقروء في المرسوم م/134. نص حكيم هو الصيغة القديمة («دفتر عائلة»)؛ الأثر غير ظاهر.</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -3062,8 +3230,16 @@
           <t>الملاحظة لا تذكر الأداة؛ نصها يطابق البند المقروء في المرسوم م/134. نص حكيم هو الصيغة القديمة («الذكور المكملين من العمر سبعة عشر عاما»)؛ الأثر غير ظاهر. عنوان البند «ثانياً» في الصفحة 2 والبند 5 في الصفحة 3.</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -3154,8 +3330,16 @@
           <t>الصفحة 1 تحمل رقم القرار وتاريخه وتحيل إلى «الصيغة المرافقة»؛ البند في صفحات الصيغة المرافقة (هيئة الخبراء) 3 و4. نص حكيم للمادة الرابعة لا يتضمن إلا الفقرة (1) ولا أثر فيه للفقرات الجديدة. صفحات 24051991 تخص القرار 367 لعام 1436هـ (إضافة فقرة (1) مكرر للمادة الرابعة) وليست الأداة المقصودة.</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3251,8 +3435,16 @@
           <t>نص حكيم ما زال «ويصدر الوزير قرارًا بتكوينها». البند (2) من «أولاً».</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3376,8 +3568,16 @@
           <t>الصيغة المرافقة تعيد نص المادة كاملًا والفرق الظاهر هو البند 8 الغائب عن hk_text. ملاحظة جانبية: صور 341624ca هي مرسوم ملكي آخر رقم م/207 وتاريخ 1445/9/28هـ نصه «2- إضافة فقرة إلى المادة (السابعة) تحمل الرقم (9) بالنص الآتي: "اللوحات المقطورة ونصف المقطورة".» وهو غير ظاهر أيضًا في hk_text، ولا يخص هذه الملاحظة. صفحة 4cdb504a_Page_024 نسخة موحدة قديمة بحاشية التعديل ولا تتضمن البند 8.</t>
         </is>
       </c>
-      <c r="T15" s="5" t="inlineStr"/>
-      <c r="U15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3475,8 +3675,16 @@
           <t>hk_text ما زال بغرامة «ألفي ريال» ودون الفقرة 2 وجملة تحريك المركبة. ملاحظة: المرسوم م/70 وتاريخ 1437/11/6هـ (صور 32a8879b) عدّل المادة نفسها سابقًا إلى «عشرة آلاف» دون الفقرة 2.</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3582,8 +3790,16 @@
           <t>hk_text ما زال بالنص الأصلي ذي البنود الأربعة وترتيب الغرامات القديم (الجدول 1 = 500-900).</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr"/>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -3673,8 +3889,16 @@
           <t>الصورة مطبوعة بآلة كاتبة قديمة منخفضة الوضوح؛ الأثر والأرقام واضحة، لكن الهمزات والتاء المربوطة/الهاء قد لا تطابق حرفيًا. نص حكيم ما زال بالنص القديم (تؤمن وسائط النقل... ثلاثة الاف ريال). لم أفحص صور الملف 6407cc0a المرفقة أيضًا لأن أداة الملاحظة وُجدت في 2ec0d2ff.</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -3768,8 +3992,16 @@
           <t>old_phrase من نص حكيم لا من الأداة. الصورة منخفضة الوضوح.</t>
         </is>
       </c>
-      <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -3859,8 +4091,16 @@
           <t>نص حكيم ما زال بالنص القديم (بمعدل بمائة ريال شهرياً).</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -3954,8 +4194,16 @@
           <t>old_phrase مأخوذة من نص حكيم (الأداة لا تقتبسها). ملاحظة: مرفق المرسوم م/9 لعام 1397هـ (البند 24) يعدل «المادة (107)» عن يومية الميدان بـ(15) ريالًا، فقد يوجد اختلاف ترقيم بين المادتين 107 و108.</t>
         </is>
       </c>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -4182,8 +4430,16 @@
           <t>الملاحظة لا تسمي الأداة؛ المرسوم م/95 (البند أولاً/2) وقرار مجلس الوزراء 489 (البند ثانياً: إلغاء المادة (3) من النظام.) كلاهما في الصور. نص المادة ما زال قائمًا في حكيم.</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -4261,8 +4517,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة العاشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -4340,8 +4604,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الحادية عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -4419,8 +4691,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الثانية عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -4498,8 +4778,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الثالثة عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -4577,8 +4865,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الرابعة عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -4656,8 +4952,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الخامسة عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -4735,8 +5039,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة السادسة عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -4814,8 +5126,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة السابعة عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -4893,8 +5213,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الثامنة عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -4972,8 +5300,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة التاسعة عشرة بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -5051,8 +5387,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة العشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -5130,8 +5474,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الحادية والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -5209,8 +5561,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الثانية والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T15" s="5" t="inlineStr"/>
-      <c r="U15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -5288,8 +5648,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الثالثة والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -5367,8 +5735,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الرابعة والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr"/>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -5446,8 +5822,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الخامسة والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -5525,8 +5909,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة السادسة والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -5604,8 +5996,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة السابعة والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -5683,8 +6083,16 @@
           <t>البند (3) من (أولاً) في الصفحة 2 يلغي الباب الرابع عشر كاملًا لا هذه المادة بعينها؛ انتماء المادة المادة الثامنة والعشرون بعد المائتين إلى الباب الرابع عشر مأخوذ من ملاحظة الهيئة لا من الصورة. نص المادة ما زال قائمًا في حكيم دون إشارة إلغاء. البند نفسه يُحِل عبارة "المحكمة العمالية أو المحاكم العمالية" محل "هيئة تسوية الخلافات العمالية أو هيئات تسوية الخلافات العمالية" في الأبواب الأخرى اعتبارًا من إنشاء المحاكم العمالية.</t>
         </is>
       </c>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -5769,8 +6177,16 @@
           <t>نص حكيم ما زال يعرض نص المادة كاملًا («تختص المحاكم التجارية بالنظر في الآتي: ...») دون أن يُعلَّم ملغى. البند نفسه في قرار مجلس الوزراء المرافق (ad08a1e9 ص4).</t>
         </is>
       </c>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -5852,8 +6268,16 @@
           <t>نص المادة (بدل السكن) ما زال قائمًا في حكيم. البند (1) من المرفق نفسه يضم بدل السكن وبدل الخادم إلى الراتب الأساسي.</t>
         </is>
       </c>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -5935,8 +6359,16 @@
           <t>نص المادة (بدل الخادم مائة ريال) ما زال قائمًا في حكيم. الإلغاء يشمل أيضًا تعديل م/9 للمادة (البند العاشر)، فملاحظة م/9 على المادة 60 (boe26-cbe36e097e882093540256da) تسقط عمليًا.</t>
         </is>
       </c>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr"/>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -6168,8 +6600,16 @@
           <t>قرار موافقة على المقر لا يعدّل نص المادة؛ تبقى الفراغات «مدينة ......... بدولة ......» في النص كما هي في المصدر، ويكفي إبقاء الملاحظة.</t>
         </is>
       </c>
-      <c r="T2" s="5" t="inlineStr"/>
-      <c r="U2" s="5" t="inlineStr"/>
+      <c r="T2" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U2" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -6251,8 +6691,16 @@
           <t>قرار تفسيري لا يعدّل النص؛ نص حكيم سليم. نص القرار أوسع من الملاحظة (يضيف "ونحوهما من العبارات الدالة على وجوب الوفاء...").</t>
         </is>
       </c>
-      <c r="T3" s="5" t="inlineStr"/>
-      <c r="U3" s="5" t="inlineStr"/>
+      <c r="T3" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U3" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
@@ -6335,8 +6783,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T4" s="5" t="inlineStr"/>
-      <c r="U4" s="5" t="inlineStr"/>
+      <c r="T4" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U4" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -6419,8 +6875,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T5" s="5" t="inlineStr"/>
-      <c r="U5" s="5" t="inlineStr"/>
+      <c r="T5" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U5" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
@@ -6502,8 +6966,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T6" s="5" t="inlineStr"/>
-      <c r="U6" s="5" t="inlineStr"/>
+      <c r="T6" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U6" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -6585,8 +7057,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T7" s="5" t="inlineStr"/>
-      <c r="U7" s="5" t="inlineStr"/>
+      <c r="T7" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U7" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -6668,8 +7148,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T8" s="5" t="inlineStr"/>
-      <c r="U8" s="5" t="inlineStr"/>
+      <c r="T8" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U8" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -6751,8 +7239,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T9" s="5" t="inlineStr"/>
-      <c r="U9" s="5" t="inlineStr"/>
+      <c r="T9" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U9" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -6834,8 +7330,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T10" s="5" t="inlineStr"/>
-      <c r="U10" s="5" t="inlineStr"/>
+      <c r="T10" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U10" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -6917,8 +7421,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T11" s="5" t="inlineStr"/>
-      <c r="U11" s="5" t="inlineStr"/>
+      <c r="T11" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U11" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -7000,8 +7512,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T12" s="5" t="inlineStr"/>
-      <c r="U12" s="5" t="inlineStr"/>
+      <c r="T12" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U12" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -7083,8 +7603,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T13" s="5" t="inlineStr"/>
-      <c r="U13" s="5" t="inlineStr"/>
+      <c r="T13" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U13" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -7166,8 +7694,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T14" s="5" t="inlineStr"/>
-      <c r="U14" s="5" t="inlineStr"/>
+      <c r="T14" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U14" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -7249,8 +7785,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T15" s="5" t="inlineStr"/>
-      <c r="U15" s="5" t="inlineStr"/>
+      <c r="T15" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U15" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -7332,8 +7876,16 @@
           <t>المرسوم يقرر تعجيل نفاذ المادة اعتبارًا من 1442/2/14هـ استثناءً من المادة (63)، ولا يعدّل نصها. المادة مذكورة بعينها في قائمة البند أولاً.</t>
         </is>
       </c>
-      <c r="T16" s="5" t="inlineStr"/>
-      <c r="U16" s="5" t="inlineStr"/>
+      <c r="T16" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U16" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -7415,8 +7967,16 @@
           <t>القرار لا يتضمن بندًا يعدّل نص المادة؛ ويدل على ذلك البند «تاسعاً : تراجع هيئة الخبراء بمجلس الوزراء مع الجهات المختصة الأنظمة التي تأثرت بالترتيبات التنظيمية الواردة في البنود السابقة، وتقترح التعديلات التي تراها مناسبة.» وفي البند رابعاً: «يرأس وزير العمل مجالس إدارات المؤسسات التالية : 1 – المؤسسة العامة للتأمينات الاجتماعية.» الملاحظة إخبارية في الهيئة؛ التعديل النصي اللاحق للتعريف جاء بأدوات أخرى.</t>
         </is>
       </c>
-      <c r="T17" s="5" t="inlineStr"/>
-      <c r="U17" s="5" t="inlineStr"/>
+      <c r="T17" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U17" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -7498,8 +8058,16 @@
           <t>أقرب بند للمادة: «رابعاً : يرأس وزير العمل مجالس إدارات المؤسسات التالية : 1 – المؤسسة العامة للتأمينات الاجتماعية.» ولا يوجد بند يعدّل نص النظام، بل «تاسعاً : تراجع هيئة الخبراء بمجلس الوزراء مع الجهات المختصة الأنظمة التي تأثرت بالترتيبات التنظيمية الواردة في البنود السابقة، وتقترح التعديلات التي تراها مناسبة.» صفحتا الرقم والبند رابعاً ليستا ضمن صور هذه الملاحظة بل ضمن صور الملاحظة boe26-5822b614ca4677df6923a6e2.</t>
         </is>
       </c>
-      <c r="T18" s="5" t="inlineStr"/>
-      <c r="U18" s="5" t="inlineStr"/>
+      <c r="T18" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U18" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -7577,8 +8145,16 @@
           <t>القرار تفسيري صراحة ولا يعدّل نصًا. التاريخ في الصورة 22/9/1397هـ والملاحظة تقول 23/9/1397هـ. القرار لا يذكر المادة (5) بعينها، بل يفسر الفقرة (ب) من المادة (4) والمادتين (26، 27)؛ فربط الملاحظة بالمادة (5) يحتاج تحقق. ملاحظة جانبية: hk_text للمادة (5) يتضمن نص «تعديلات المادة» ملصقًا داخل نص المادة.</t>
         </is>
       </c>
-      <c r="T19" s="5" t="inlineStr"/>
-      <c r="U19" s="5" t="inlineStr"/>
+      <c r="T19" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U19" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -7660,8 +8236,16 @@
           <t>قرار تفسيري: الحيثيات تنص «ومن المستحسن ان يصدر بهذا قرار تفسيري من مجلس الوزراء»، ومنطوقه يُلحق حالة فتح شارع جديد بحالة توسيع الطريق الضيقة في المادتين (11) و(12) دون تعديل نصهما؛ فلا أثر نصي مطلوب في حكيم. صفحة المنطوق باهتة الحبر وبعض حروفها («فتح شارع»، «توسيع طريق ضيقة») مقروءة بصعوبة، ورقم القرار بخط اليد.</t>
         </is>
       </c>
-      <c r="T20" s="5" t="inlineStr"/>
-      <c r="U20" s="5" t="inlineStr"/>
+      <c r="T20" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U20" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
@@ -7743,8 +8327,16 @@
           <t>قرار تفسيري: الحيثيات تنص «ومن المستحسن ان يصدر بهذا قرار تفسيري من مجلس الوزراء»، ومنطوقه يُلحق حالة فتح شارع جديد بحالة توسيع الطريق الضيقة في المادتين (11) و(12) دون تعديل نصهما؛ فلا أثر نصي مطلوب في حكيم. صفحة المنطوق باهتة الحبر وبعض حروفها («فتح شارع»، «توسيع طريق ضيقة») مقروءة بصعوبة، ورقم القرار بخط اليد.</t>
         </is>
       </c>
-      <c r="T21" s="5" t="inlineStr"/>
-      <c r="U21" s="5" t="inlineStr"/>
+      <c r="T21" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U21" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -7826,8 +8418,16 @@
           <t>القرار يضع «قواعد تتبع في تنفيذ» المادة (21) (تقسيم الأراضي ومخططات التقسيم ونسبة الاقتطاع 33%) ولا يعيد صياغة نص المادة؛ فهو إجراء/قواعد تنفيذية لا تمس نص المادة في حكيم. مع أن الحيثيات تذكر أن «الوزارة تقترح تعديل المادتين (21 و 23)»، فالمنطوق جاء بصيغة قواعد تنفيذ؛ قد يرغب المالك في إلحاق القواعد كملاحظة. الصور مطبوعة بالآلة الكاتبة وبعض الأسطر باهتة.</t>
         </is>
       </c>
-      <c r="T22" s="5" t="inlineStr"/>
-      <c r="U22" s="5" t="inlineStr"/>
+      <c r="T22" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U22" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="4" t="inlineStr">
@@ -7909,8 +8509,16 @@
           <t>القرار يضع قواعد تنفيذ للمادة (23) (اتساعات الشوارع: 15 متراً للرئيسية، 12 و10 للثانوية، 6 و5 أمتار للفرعية والأزقة، ومرجعية وزير الداخلية) دون إعادة صياغة نص المادة؛ نص حكيم ما زال بالاتساعات الأصلية (15، 8-12، 4-6). يحتمل أن تُعدّ هذه القواعد معدِّلة فعليًا للاتساعات؛ يستحسن عرضها على المالك. الصفحة 3 (الفقرة ج) باهتة جدًا.</t>
         </is>
       </c>
-      <c r="T23" s="5" t="inlineStr"/>
-      <c r="U23" s="5" t="inlineStr"/>
+      <c r="T23" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U23" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -7992,8 +8600,16 @@
           <t>القرار يقرر تطبيق النظام على الكلية ولا يعدّل نص المادة (1) ولا يضيف إليها بندًا بنصه؛ يكفي إبقاؤه ملاحظة على المادة دون مساس بنصها.</t>
         </is>
       </c>
-      <c r="T24" s="5" t="inlineStr"/>
-      <c r="U24" s="5" t="inlineStr"/>
+      <c r="T24" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U24" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -8075,8 +8691,16 @@
           <t>رأيت البند بعينه؛ المرسوم يمدد المدة (سنتين) سنة إضافية دون تعديل نص المادة. ديباجة القرار 360 تذكر أن المهلة "(سنة واحدة) تنتهي بتاريخ 1445/2/19هـ". نص حكيم سليم ولا يحتاج تعديلًا؛ يكفي إظهار الملاحظة.</t>
         </is>
       </c>
-      <c r="T25" s="5" t="inlineStr"/>
-      <c r="U25" s="5" t="inlineStr"/>
+      <c r="T25" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U25" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -8158,8 +8782,16 @@
           <t>قرار تفسيري لا يعدّل النص. تعارض في الترقيم: الملاحظة مدرجة تحت «المادة (189)» بينما الصورة تسمي المادة ذات النص «الشرح على الصكوك الصادرة لدى غيره من كتاب العدل...» بالمادة (186) — قرأت الرقم 186 مرتين في الصورة لكنه مكتوب على آلة كاتبة رديئة. الرقم 1424 والتاريخ بخط اليد. كلمة «تعارض» في سطر القرار تبدو على الآلة الكاتبة كـ«تعارب»، ونُقلت «تعارض» استنادًا إلى السطر الأول من الديباجة الذي يقرأ «عن وجود تعارض» بوضوح.</t>
         </is>
       </c>
-      <c r="T26" s="5" t="inlineStr"/>
-      <c r="U26" s="5" t="inlineStr"/>
+      <c r="T26" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U26" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -8242,8 +8874,16 @@
           <t>القرار يقرر صراحة عدم الحاجة إلى تعديل النظام؛ لا أثر على النص، ونص المادة في حكيم مطابق لنص الهيئة. رقم القرار وتاريخه مكتوبان بخط اليد.</t>
         </is>
       </c>
-      <c r="T27" s="5" t="inlineStr"/>
-      <c r="U27" s="5" t="inlineStr"/>
+      <c r="T27" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U27" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -8326,8 +8966,16 @@
           <t>القرار مقروء كاملًا، ولا يتضمن صيغة تعديل لنص المادة؛ هو قرار تحديد مرفق بموجب التفويض الوارد في المادة نفسها («والمرافق الأخرى التي يصدر بتحديدها قرار من مجلس الوزراء»). ملاحظة الهيئة تصفه بأنه تعديل «يضاف اليها النص الآتي»؛ فإن أُريد إثبات أثره فبوصفه حاشية لا تغييرًا في نص المادة — يحسمه المالك.</t>
         </is>
       </c>
-      <c r="T28" s="5" t="inlineStr"/>
-      <c r="U28" s="5" t="inlineStr"/>
+      <c r="T28" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U28" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -8409,8 +9057,16 @@
           <t>حكم استثنائي مستقل لا يعدل صياغة المادة؛ يُحفظ ملاحظةً على المادة لا نصًا بديلًا. already_in_hakeem=false بمعنى أن الاستثناء غير مذكور في نص المادة، وهذا متوقع.</t>
         </is>
       </c>
-      <c r="T29" s="5" t="inlineStr"/>
-      <c r="U29" s="5" t="inlineStr"/>
+      <c r="T29" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U29" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -8492,8 +9148,16 @@
           <t>المرسوم ينفذ زيادة رأس المال ولا يعدّل نص المادة. قرار مجلس الوزراء المرافق (رقم 1059 وتاريخ 1395/11/13هـ كما يبدو بخط اليد) ينص: «زيادة رأسمال صندوق التنمية الصناعية السعودى بمبلغ (2,500,000,000) الفين وخمسمائة مليون ريال ليصبح رأسمال الصندوق بعد الزيادة (3,000,000,000) ثلاثة آلاف مليون ريال سعودى». الأرقام في الصورة مكتوبة بفواصل «ر» (٢ر٥٠٠ر٠٠٠ر٠٠٠) وحُوّلت إلى أرقام غربية. رقم المرسوم وتاريخه بخط اليد لكنهما مقروءان.</t>
         </is>
       </c>
-      <c r="T30" s="5" t="inlineStr"/>
-      <c r="U30" s="5" t="inlineStr"/>
+      <c r="T30" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U30" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -8577,8 +9241,16 @@
           <t>مع أن الحيثيات تذكر طلب «الموافقة على تعديل نص المادة (السابعة)»، فالمنطوق لم يعدّل النص بل قرّر حكمًا لمعاملة نائب الرئيس؛ فلا أثر نصي مطلوب في حكيم، ونص المادة في حكيم يطابق النص المقتبس في الحيثيات.</t>
         </is>
       </c>
-      <c r="T31" s="5" t="inlineStr"/>
-      <c r="U31" s="5" t="inlineStr"/>
+      <c r="T31" s="5" t="inlineStr">
+        <is>
+          <t>موافق</t>
+        </is>
+      </c>
+      <c r="U31" s="5" t="inlineStr">
+        <is>
+          <t>موافقة المالك 23/10/2026: «موافق على كل البنود»</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <dataValidations count="1">
